--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/TENNESSEE_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/TENNESSEE_2017.xlsx
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C175">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C297">
@@ -10417,7 +10417,7 @@
         <v>112</v>
       </c>
       <c r="D559">
-        <v>0.009942299156679981</v>
+        <v>0.00994229915667998</v>
       </c>
     </row>
     <row r="560">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C762">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C763">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C797">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C798">
